--- a/artfynd/A 59291-2022 artfynd.xlsx
+++ b/artfynd/A 59291-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59291-2022 artfynd.xlsx
+++ b/artfynd/A 59291-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106057082</v>
+        <v>106057439</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norr om Gubbmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497026.5777066239</v>
+        <v>497002</v>
       </c>
       <c r="R2" t="n">
-        <v>7004727.232315147</v>
+        <v>7004719</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,24 +750,14 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Revlummer i äldre granskog. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
+          <t>Gott om skrovellav på en sälg där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +777,32 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. Fältskikt med risväxter och inslag av högörter. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
+          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. I beståndet finns gott om klenvuxna granar. Fältskikt med risväxter och inslag av högörter. Buskskikt med enbuskar. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>En gammal levande tvåstammig sälg som delvis är skadad och utgörs av död ved. Ena stammen har en brösthöjdsdiameter på 30 cm. Vedsvampar lever i sälgen som står i luckig och ljusöppen miljö nära kanten till ett kalhygge.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal levande tvåstammig sälg som delvis är skadad och utgörs av död ved. Ena stammen har en brösthöjdsdiameter på 30 cm. Vedsvampar lever i sälgen som står i luckig och ljusöppen miljö nära kan</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,46 +820,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106057207</v>
+        <v>106057893</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497001.690820115</v>
+        <v>496955</v>
       </c>
       <c r="R3" t="n">
-        <v>7004718.672523675</v>
+        <v>7004651</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,24 +891,14 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lunglav på en sälg där det även växer skrovellav. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
+          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,32 +918,32 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. Fältskikt med risväxter och inslag av högörter. Buskskikt med enbuskar. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
+          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. I beståndet finns gott om klenvuxna granar. Fältskikt med risväxter och inslag av gräs och högörter. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>En gammal levande tvåstammig sälg som delvis är skadad och utgörs av död ved. Ena stammen har en brösthöjdsdiameter på 30 cm. Vedsvampar lever i sälgen som står i luckig och ljusöppen miljö nära kanten till ett kalhygge.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal levande tvåstammig sälg som delvis är skadad och utgörs av död ved. Ena stammen har en brösthöjdsdiameter på 30 cm. Vedsvampar lever i sälgen som står i luckig och ljusöppen miljö nära kan</t>
+          <t>Branch on living tree # Även gren på död gran. # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -971,46 +961,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106057439</v>
+        <v>106058872</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1018,10 +999,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497001.690820115</v>
+        <v>496920</v>
       </c>
       <c r="R4" t="n">
-        <v>7004718.672523675</v>
+        <v>7004596</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1051,24 +1032,14 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om skrovellav på en sälg där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
+          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1088,32 +1059,32 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. I beståndet finns gott om klenvuxna granar. Fältskikt med risväxter och inslag av högörter. Buskskikt med enbuskar. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
+          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. I beståndet finns gott om klenvuxna granar. Fältskikt med risväxter och inslag av gräs och högörter. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>En gammal levande tvåstammig sälg som delvis är skadad och utgörs av död ved. Ena stammen har en brösthöjdsdiameter på 30 cm. Vedsvampar lever i sälgen som står i luckig och ljusöppen miljö nära kanten till ett kalhygge.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal levande tvåstammig sälg som delvis är skadad och utgörs av död ved. Ena stammen har en brösthöjdsdiameter på 30 cm. Vedsvampar lever i sälgen som står i luckig och ljusöppen miljö nära kan</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1131,19 +1102,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106057893</v>
+        <v>106058883</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1174,10 +1140,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496954.5830821627</v>
+        <v>496877</v>
       </c>
       <c r="R5" t="n">
-        <v>7004650.957002977</v>
+        <v>7004576</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1207,19 +1173,9 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-01-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1269,7 +1225,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Även gren på död gran. # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1287,43 +1243,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106058875</v>
+        <v>106057207</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1331,10 +1285,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496883.9177769624</v>
+        <v>497002</v>
       </c>
       <c r="R6" t="n">
-        <v>7004549.382352658</v>
+        <v>7004719</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1364,24 +1318,14 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Revlummer intill en äldre gran i gammal granskog. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
+          <t>Lunglav på en sälg där det även växer skrovellav. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1401,7 +1345,32 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. I beståndet finns gott om klenvuxna granar. Fältskikt med risväxter och inslag av gräs och högörter. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
+          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. Fältskikt med risväxter och inslag av högörter. Buskskikt med enbuskar. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>En gammal levande tvåstammig sälg som delvis är skadad och utgörs av död ved. Ena stammen har en brösthöjdsdiameter på 30 cm. Vedsvampar lever i sälgen som står i luckig och ljusöppen miljö nära kanten till ett kalhygge.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal levande tvåstammig sälg som delvis är skadad och utgörs av död ved. Ena stammen har en brösthöjdsdiameter på 30 cm. Vedsvampar lever i sälgen som står i luckig och ljusöppen miljö nära kan</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1419,15 +1388,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106058883</v>
+        <v>106058645</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,26 +1399,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1462,10 +1430,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496877.6103494666</v>
+        <v>496911</v>
       </c>
       <c r="R7" t="n">
-        <v>7004576.041532566</v>
+        <v>7004639</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1495,24 +1463,14 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
+          <t>Ymnig påväxt av lunglav på en mycket grov gammal sälg. Flertalet lunglavsbålar är fertila med apothecier. Här växer även lunglav på gran intill sälgen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1527,37 +1485,37 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. I beståndet finns gott om klenvuxna granar. Fältskikt med risväxter och inslag av gräs och högörter. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
+          <t>Mark som på 1960-talet delvis varit öppen omkring den gamla sälgen, sedan beskogats och på senare år har skogen här avverkats och enstaka små trädgrupper lämnats kvar.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En mycket grov, gammal och vidkronig sälg med 120 cm i brösthöjdsdiameter. Delar av trädet består av död ved där t.ex. stambasens inre utgörs av murken ved. Tätt inpå sälgen står några granar.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En mycket grov, gammal och vidkronig sälg med 120 cm i brösthöjdsdiameter. Delar av trädet består av död ved där t.ex. stambasens inre utgörs av murken ved. Tätt inpå sälgen står några granar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1575,53 +1533,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106058872</v>
+        <v>106057082</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr om Gubbmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496920.1516202303</v>
+        <v>497027</v>
       </c>
       <c r="R8" t="n">
-        <v>7004595.877471988</v>
+        <v>7004727</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1651,24 +1609,14 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
+          <t>Revlummer i äldre granskog. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1688,32 +1636,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. I beståndet finns gott om klenvuxna granar. Fältskikt med risväxter och inslag av gräs och högörter. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. Fältskikt med risväxter och inslag av högörter. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1728,6 +1651,123 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>106058875</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norr om Gubbmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>496884</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7004549</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-01-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-01-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Revlummer intill en äldre gran i gammal granskog. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 59291-2022.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och död ved förekommer i måttlig mängd. I beståndet finns gott om klenvuxna granar. Fältskikt med risväxter och inslag av gräs och högörter. Vid observationstillfället var skogen här extra luckig p.g.a. röjning utförd i närtid.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59291-2022 artfynd.xlsx
+++ b/artfynd/A 59291-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -817,6 +822,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106057439</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -958,6 +968,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106057893</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1099,6 +1114,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106058872</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1240,6 +1260,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106058883</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1385,6 +1410,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106057207</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1530,6 +1560,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106058645</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1651,6 +1686,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106057082</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1768,8 +1808,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106058875</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>